--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -134,6 +134,22 @@
   </si>
   <si>
     <t>NOT_EXECUTED</t>
+  </si>
+  <si>
+    <t>AUTH-004</t>
+  </si>
+  <si>
+    <t>ログアウト</t>
+  </si>
+  <si>
+    <t>ログインしている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ログアウトボタンを押す
+2. 確認ダイアログで「はい」を選択する</t>
+  </si>
+  <si>
+    <t>• ログアウトに成功し、ログイン画面に遷移する</t>
   </si>
   <si>
     <t>USER-001</t>
@@ -725,12 +741,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
@@ -867,7 +883,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>34</v>
       </c>
@@ -875,48 +891,48 @@
         <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>44</v>
@@ -927,13 +943,45 @@
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="containsText" dxfId="0" priority="1">
       <formula>NOT(ISERROR(SEARCH("FAIL",J2)))</formula>
     </cfRule>
@@ -945,7 +993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -961,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1038,7 +1086,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>34</v>
@@ -1046,33 +1094,53 @@
       <c r="C5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>37</v>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>19</v>
+      <c r="F5" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1085,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1113,19 +1181,19 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1142,19 +1210,19 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1171,19 +1239,19 @@
         <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1200,19 +1268,19 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1222,55 +1290,84 @@
       <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>56</v>
+      <c r="E7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1306,16 +1403,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1332,16 +1429,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>12</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -152,6 +152,9 @@
     <t>• ログアウトに成功し、ログイン画面に遷移する</t>
   </si>
   <si>
+    <t>SKIP</t>
+  </si>
+  <si>
     <t>USER-001</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
   </si>
   <si>
     <t>セキュリティテスト環境の準備待ち</t>
+  </si>
+  <si>
+    <t>多要素認証は次リリースで実装予定のためスキップ</t>
   </si>
   <si>
     <t>yamada</t>
@@ -260,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -285,8 +291,12 @@
       <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +331,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -361,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -384,10 +399,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -911,37 +929,37 @@
       <c r="I5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>33</v>
+      <c r="J5" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="D6" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>19</v>
@@ -949,31 +967,31 @@
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="D7" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>33</v>
@@ -1009,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1100,22 +1118,22 @@
       <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
+      <c r="F5" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>42</v>
+      <c r="D6" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -1126,16 +1144,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>22</v>
@@ -1181,19 +1199,19 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1210,19 +1228,19 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1239,19 +1257,19 @@
         <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1268,19 +1286,19 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1293,81 +1311,81 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>33</v>
+      <c r="D5" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1403,44 +1421,44 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
     </row>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -5,16 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="テストケース一覧" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="要件別テストケース" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="実行結果" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="FAIL一覧" state="visible" r:id="rId7"/>
+    <sheet sheetId="2" name="FAIL一覧" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -44,6 +42,15 @@
   </si>
   <si>
     <t>実行ステータス</t>
+  </si>
+  <si>
+    <t>担当者</t>
+  </si>
+  <si>
+    <t>完了日時</t>
+  </si>
+  <si>
+    <t>メモ</t>
   </si>
   <si>
     <t>AUTH-001</t>
@@ -82,6 +89,15 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>onawa</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:00:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>AUTH-002</t>
   </si>
   <si>
@@ -109,6 +125,12 @@
     <t>FAIL</t>
   </si>
   <si>
+    <t>2026-05-11T10:30:00</t>
+  </si>
+  <si>
+    <t>パスワード試行失敗カウントがインクリメントされない不具合</t>
+  </si>
+  <si>
     <t>AUTH-003</t>
   </si>
   <si>
@@ -136,6 +158,9 @@
     <t>NOT_EXECUTED</t>
   </si>
   <si>
+    <t>セキュリティテスト環境の準備待ち</t>
+  </si>
+  <si>
     <t>AUTH-004</t>
   </si>
   <si>
@@ -153,6 +178,9 @@
   </si>
   <si>
     <t>SKIP</t>
+  </si>
+  <si>
+    <t>多要素認証は次リリースで実装予定のためスキップ</t>
   </si>
   <si>
     <t>USER-001</t>
@@ -185,6 +213,12 @@
 • DBに更新日時が記録される</t>
   </si>
   <si>
+    <t>yamada</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:00:00</t>
+  </si>
+  <si>
     <t>USER-002</t>
   </si>
   <si>
@@ -204,62 +238,10 @@
 • DBへの更新は行われない</t>
   </si>
   <si>
-    <t>テストケースID</t>
-  </si>
-  <si>
-    <t>担当者</t>
-  </si>
-  <si>
-    <t>完了日時</t>
-  </si>
-  <si>
-    <t>エビデンス</t>
-  </si>
-  <si>
     <t>不具合ID</t>
   </si>
   <si>
-    <t>メモ</t>
-  </si>
-  <si>
-    <t>onawa</t>
-  </si>
-  <si>
-    <t>2026-05-11T10:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence/AUTH-001/login-screen.png
-evidence/AUTH-001/dashboard-redirect.png</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-05-11T10:30:00</t>
-  </si>
-  <si>
-    <t>evidence/AUTH-002/error-message.png</t>
-  </si>
-  <si>
     <t>BUG-192</t>
-  </si>
-  <si>
-    <t>パスワード試行失敗カウントがインクリメントされない不具合</t>
-  </si>
-  <si>
-    <t>セキュリティテスト環境の準備待ち</t>
-  </si>
-  <si>
-    <t>多要素認証は次リリースで実装予定のためスキップ</t>
-  </si>
-  <si>
-    <t>yamada</t>
-  </si>
-  <si>
-    <t>2026-05-11T11:00:00</t>
-  </si>
-  <si>
-    <t>evidence/USER-001/profile-update.png</t>
   </si>
 </sst>
 </file>
@@ -759,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -771,9 +753,12 @@
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="9" width="52" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,201 +789,264 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="F3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>19</v>
+      <c r="G5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5" t="s">
+    <row r="6" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="K6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="7" ht="54" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="G7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>33</v>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:M1"/>
   <conditionalFormatting sqref="J2:J7">
     <cfRule type="containsText" dxfId="0" priority="1">
       <formula>NOT(ISERROR(SEARCH("FAIL",J2)))</formula>
@@ -1010,392 +1058,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1421,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1438,28 +1100,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -92,7 +92,9 @@
     <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
   </si>
   <si>
-    <t>1. ログイン画面を開く 2. 有効なIDと誤ったPWで5回連続ログインを試みる 3. 6回目のログインを試みる</t>
+    <t xml:space="preserve">1. ログイン画面を開く
+2. 有効なIDと誤ったPWで5回連続ログインを試みる
+3. 6回目のログインを試みる</t>
   </si>
   <si>
     <t>5回失敗後にアカウントがロックされる。「アカウントがロックされています」メッセージが表示される。正しい認証情報でもログイン不可となる。</t>
@@ -664,7 +666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>TC-ID</t>
   </si>
@@ -84,23 +84,6 @@
   </si>
   <si>
     <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
-  </si>
-  <si>
-    <t>TC-003</t>
-  </si>
-  <si>
-    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. ログイン画面を開く
-2. 有効なIDと誤ったPWで5回連続ログインを試みる
-3. 6回目のログインを試みる</t>
-  </si>
-  <si>
-    <t>5回失敗後にアカウントがロックされる。「アカウントがロックされています」メッセージが表示される。正しい認証情報でもログイン不可となる。</t>
-  </si>
-  <si>
-    <t>ロックアウト閾値=5回を前提とする</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -546,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -666,7 +649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -686,7 +669,7 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -698,41 +681,6 @@
         <v>18</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -778,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>9</v>
@@ -786,7 +734,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>TC-ID</t>
   </si>
@@ -86,6 +86,23 @@
     <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
   </si>
   <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ログイン画面を開く
+2. 有効なIDと誤ったPWで5回連続ログインを試みる
+3. 6回目のログインを試みる</t>
+  </si>
+  <si>
+    <t>5回失敗後にアカウントがロックされる。「アカウントがロックされています」メッセージが表示される。正しい認証情報でもログイン不可となる。</t>
+  </si>
+  <si>
+    <t>ロックアウト閾値=5回を前提とする</t>
+  </si>
+  <si>
     <t>TC-004</t>
   </si>
   <si>
@@ -96,6 +113,38 @@
   </si>
   <si>
     <t>ログイン画面へ遷移する。セッションが破棄される。</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>正常系：プロフィール更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ヘッダーのユーザーアイコン→「プロフィール編集」を選択する
+2. 氏名を「山田 花子」に変更する
+3. メールアドレスを「hanako@example.com」に変更する
+4. 「保存」ボタンを押下する</t>
+  </si>
+  <si>
+    <t>「プロフィールを更新しました」成功メッセージが表示される。変更した氏名・メールアドレスが画面に反映される。DBに更新日時が記録される。</t>
+  </si>
+  <si>
+    <t>DD-002</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>異常系：無効メールアドレスへの更新バリデーション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. プロフィール編集画面を開く
+2. メールアドレスフィールドに「not-an-email」を入力する
+3. 「保存」ボタンを押下する</t>
+  </si>
+  <si>
+    <t>保存が拒否される。「有効なメールアドレスを入力してください」バリデーションエラーが表示される。DBへの更新は行われない。</t>
   </si>
   <si>
     <t>不具合ID</t>
@@ -529,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -649,7 +698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -669,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -681,6 +730,111 @@
         <v>18</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -726,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>9</v>
@@ -734,7 +888,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
   <si>
     <t>TC-ID</t>
   </si>
@@ -84,23 +84,6 @@
   </si>
   <si>
     <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
-  </si>
-  <si>
-    <t>TC-003</t>
-  </si>
-  <si>
-    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. ログイン画面を開く
-2. 有効なIDと誤ったPWで5回連続ログインを試みる
-3. 6回目のログインを試みる</t>
-  </si>
-  <si>
-    <t>5回失敗後にアカウントがロックされる。「アカウントがロックされています」メッセージが表示される。正しい認証情報でもログイン不可となる。</t>
-  </si>
-  <si>
-    <t>ロックアウト閾値=5回を前提とする</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -578,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -698,7 +681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -718,7 +701,7 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -733,24 +716,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>18</v>
@@ -768,7 +751,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -785,7 +768,7 @@
         <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -800,41 +783,6 @@
         <v>18</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -880,7 +828,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>9</v>
@@ -888,7 +836,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>TC-ID</t>
   </si>
@@ -84,6 +84,23 @@
   </si>
   <si>
     <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ログイン画面を開く
+2. 有効なIDと誤ったPWで5回連続ログインを試みる
+3. 6回目のログインを試みる</t>
+  </si>
+  <si>
+    <t>5回失敗後にアカウントがロックされる。「アカウントがロックされています」メッセージが表示される。正しい認証情報でもログイン不可となる。</t>
+  </si>
+  <si>
+    <t>ロックアウト閾値=5回を前提とする</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -561,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -681,7 +698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -701,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -716,24 +733,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>18</v>
@@ -751,7 +768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -768,7 +785,7 @@
         <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -783,6 +800,41 @@
         <v>18</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -828,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>9</v>
@@ -836,7 +888,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>TC-ID</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>ログイン画面へ遷移する。セッションが破棄される。</t>
+  </si>
+  <si>
+    <t>TC-002完了後に実施</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -753,7 +756,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>18</v>
@@ -770,22 +773,22 @@
     </row>
     <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -805,22 +808,22 @@
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>18</v>
@@ -880,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>9</v>
@@ -888,7 +891,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
   <si>
     <t>TC-ID</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>完了日時</t>
-  </si>
-  <si>
-    <t>メモ</t>
   </si>
   <si>
     <t>実行ステータス</t>
@@ -581,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -592,11 +589,10 @@
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,222 +623,201 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="4" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
+    <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="4" t="s">
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -850,7 +825,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -860,10 +835,9 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,22 +857,19 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>TC-ID</t>
   </si>
@@ -65,22 +65,28 @@
     <t>smoke</t>
   </si>
   <si>
+    <t>roonawa</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>NOT_EXECUTED</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>異常系：誤パスワードによるログイン失敗</t>
+  </si>
+  <si>
+    <t>1. ログイン画面を開く 2. 有効なユーザーIDを入力する 3. 誤ったパスワード（例: "wrongpass123"）を入力する 4. ログインボタンを押下する</t>
+  </si>
+  <si>
+    <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>NOT_EXECUTED</t>
-  </si>
-  <si>
-    <t>TC-002</t>
-  </si>
-  <si>
-    <t>異常系：誤パスワードによるログイン失敗</t>
-  </si>
-  <si>
-    <t>1. ログイン画面を開く 2. 有効なユーザーIDを入力する 3. 誤ったパスワード（例: "wrongpass123"）を入力する 4. ログインボタンを押下する</t>
-  </si>
-  <si>
-    <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
   </si>
   <si>
     <t>TC-003</t>
@@ -650,170 +656,170 @@
         <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -857,15 +863,15 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>TC-ID</t>
   </si>
@@ -23,6 +23,9 @@
     <t>種別</t>
   </si>
   <si>
+    <t>優先度</t>
+  </si>
+  <si>
     <t>手順</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>画面</t>
   </si>
   <si>
+    <t>高</t>
+  </si>
+  <si>
     <t>1. ログイン画面を開く 2. 有効なユーザーIDを入力する 3. 正しいパスワードを入力する 4. ログインボタンを押下する</t>
   </si>
   <si>
@@ -71,7 +77,7 @@
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>NOT_EXECUTED</t>
+    <t>PASS</t>
   </si>
   <si>
     <t>TC-002</t>
@@ -89,10 +95,16 @@
     <t/>
   </si>
   <si>
+    <t>FAIL</t>
+  </si>
+  <si>
     <t>TC-003</t>
   </si>
   <si>
     <t>セキュリティ：アカウントロックアウト（連続失敗）</t>
+  </si>
+  <si>
+    <t>中</t>
   </si>
   <si>
     <t xml:space="preserve">1. ログイン画面を開く
@@ -104,6 +116,9 @@
   </si>
   <si>
     <t>ロックアウト閾値=5回を前提とする</t>
+  </si>
+  <si>
+    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -154,16 +169,13 @@
   </si>
   <si>
     <t>不具合ID</t>
-  </si>
-  <si>
-    <t>(FAILなし)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -177,11 +189,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,12 +211,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFF0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -243,6 +274,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -584,21 +624,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="52" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,201 +669,222 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
+      <c r="H3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
+    <row r="4" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
+    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="6" ht="72" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -831,19 +892,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,28 +915,49 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
   <si>
     <t>TC-ID</t>
   </si>
@@ -59,7 +59,10 @@
     <t>高</t>
   </si>
   <si>
-    <t>1. ログイン画面を開く 2. 有効なユーザーIDを入力する 3. 正しいパスワードを入力する 4. ログインボタンを押下する</t>
+    <t xml:space="preserve">1. ログイン画面を開く
+2. 有効なユーザーIDを入力する
+3. 正しいパスワードを入力する
+4. ログインボタンを押下する</t>
   </si>
   <si>
     <t>/dashboard へリダイレクトされる。セッションCookieが生成される。ヘッダーにユーザー名が表示される。</t>
@@ -86,7 +89,10 @@
     <t>異常系：誤パスワードによるログイン失敗</t>
   </si>
   <si>
-    <t>1. ログイン画面を開く 2. 有効なユーザーIDを入力する 3. 誤ったパスワード（例: "wrongpass123"）を入力する 4. ログインボタンを押下する</t>
+    <t xml:space="preserve">1. ログイン画面を開く
+2. 有効なユーザーIDを入力する
+3. 誤ったパスワード（例: "wrongpass123"）を入力する
+4. ログインボタンを押下する</t>
   </si>
   <si>
     <t>ログインが拒否されダッシュボードへ遷移しない。「IDまたはパスワードが正しくありません」エラーが表示される。パスワード失敗カウントがインクリメントされる。</t>
@@ -118,9 +124,6 @@
     <t>ロックアウト閾値=5回を前提とする</t>
   </si>
   <si>
-    <t>NOT_EXECUTED</t>
-  </si>
-  <si>
     <t>TC-004</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
   </si>
   <si>
     <t>TC-002完了後に実施</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>DD-002</t>
+  </si>
+  <si>
+    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -175,7 +184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -193,11 +202,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,6 +235,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -262,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -282,7 +300,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -708,7 +729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -774,16 +795,16 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>34</v>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
@@ -792,25 +813,25 @@
         <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -844,16 +865,16 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>34</v>
+      <c r="K6" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>13</v>
@@ -862,10 +883,10 @@
         <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>44</v>
@@ -879,8 +900,8 @@
       <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>34</v>
+      <c r="K7" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -927,32 +948,32 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="F2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
     </row>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>TC-ID</t>
   </si>
@@ -130,7 +130,8 @@
     <t>正常系：ログアウト</t>
   </si>
   <si>
-    <t>1. ログイン済みの状態でログアウトボタンを押す 2. 確認ダイアログで「はい」を選択する</t>
+    <t xml:space="preserve">1. ログイン済みの状態でログアウトボタンを押す
+2. 確認ダイアログで「はい」を選択する</t>
   </si>
   <si>
     <t>ログイン画面へ遷移する。セッションが破棄される。</t>
@@ -139,7 +140,7 @@
     <t>TC-002完了後に実施</t>
   </si>
   <si>
-    <t>SKIP</t>
+    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -158,9 +159,6 @@
   </si>
   <si>
     <t>DD-002</t>
-  </si>
-  <si>
-    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -184,7 +182,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -202,15 +200,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,11 +229,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF4444"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -300,10 +289,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -799,7 +785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -865,16 +851,16 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>45</v>
+      <c r="K6" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>13</v>
@@ -883,10 +869,10 @@
         <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>44</v>
@@ -900,8 +886,8 @@
       <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>45</v>
+      <c r="K7" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -948,32 +934,32 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="F2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>26</v>
       </c>
     </row>

--- a/reports/latest/test-report.xlsx
+++ b/reports/latest/test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
   <si>
     <t>TC-ID</t>
   </si>
@@ -140,7 +140,7 @@
     <t>TC-002完了後に実施</t>
   </si>
   <si>
-    <t>NOT_EXECUTED</t>
+    <t>WAITING</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>保存が拒否される。「有効なメールアドレスを入力してください」バリデーションエラーが表示される。DBへの更新は行われない。</t>
+  </si>
+  <si>
+    <t>NOT_EXECUTED</t>
   </si>
   <si>
     <t>不具合ID</t>
@@ -887,7 +890,7 @@
         <v>26</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
